--- a/data/stocks examples/stocks tt.xlsx
+++ b/data/stocks examples/stocks tt.xlsx
@@ -14,15 +14,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="211">
-  <si>
-    <t>Наличие рисунков по ткани на 19 июня 2026 г.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="225">
+  <si>
+    <t>Наличие рисунков по ткани на 10 июля 2026 г.</t>
   </si>
   <si>
     <t>Контакты</t>
   </si>
   <si>
-    <t>Напечатано: 19 июня 2026 г. 11:04:44</t>
+    <t>Напечатано: 10 июля 2026 г. 09:43:20</t>
   </si>
   <si>
     <t>Производство: г. Иваново, ул. Тимирязева, д 1. Тел. +7(4932) 34-50-19</t>
@@ -49,7 +49,16 @@
     <t>512-1</t>
   </si>
   <si>
-    <t>237,6</t>
+    <t>168,6</t>
+  </si>
+  <si>
+    <t>Водопад</t>
+  </si>
+  <si>
+    <t>532-1</t>
+  </si>
+  <si>
+    <t>615,2</t>
   </si>
   <si>
     <t>Манхеттен</t>
@@ -76,7 +85,7 @@
     <t>554-1</t>
   </si>
   <si>
-    <t>3 071,1</t>
+    <t>2 708,1</t>
   </si>
   <si>
     <t>Одуванчики</t>
@@ -85,7 +94,7 @@
     <t>624-1</t>
   </si>
   <si>
-    <t>1 795,5</t>
+    <t>1 630,5</t>
   </si>
   <si>
     <t>Одуванчики (комп.)</t>
@@ -94,7 +103,7 @@
     <t>625-1</t>
   </si>
   <si>
-    <t>1 509,5</t>
+    <t>1 410,5</t>
   </si>
   <si>
     <t>Исландия</t>
@@ -103,10 +112,13 @@
     <t>761-1</t>
   </si>
   <si>
+    <t>143,5</t>
+  </si>
+  <si>
     <t>761-2</t>
   </si>
   <si>
-    <t>391,8</t>
+    <t>358,8</t>
   </si>
   <si>
     <t>Сердцеедка</t>
@@ -115,7 +127,7 @@
     <t>812-1</t>
   </si>
   <si>
-    <t>397,9</t>
+    <t>232,9</t>
   </si>
   <si>
     <t>Сердцеедка комп</t>
@@ -124,7 +136,7 @@
     <t>813-1</t>
   </si>
   <si>
-    <t>356,5</t>
+    <t>224,5</t>
   </si>
   <si>
     <t>Аниме комп</t>
@@ -157,25 +169,13 @@
     <t>884-1</t>
   </si>
   <si>
-    <t>269,9</t>
-  </si>
-  <si>
-    <t>Паркет</t>
-  </si>
-  <si>
-    <t>984-1</t>
-  </si>
-  <si>
-    <t>332,7</t>
-  </si>
-  <si>
-    <t>Полоски</t>
-  </si>
-  <si>
-    <t>985-1</t>
-  </si>
-  <si>
-    <t>300,2</t>
+    <t>203,9</t>
+  </si>
+  <si>
+    <t>Тэфи (комп)</t>
+  </si>
+  <si>
+    <t>885-1</t>
   </si>
   <si>
     <t>Пластер</t>
@@ -184,7 +184,7 @@
     <t>987-1</t>
   </si>
   <si>
-    <t>596,3</t>
+    <t>530,3</t>
   </si>
   <si>
     <t>абрикос</t>
@@ -193,427 +193,466 @@
     <t>1 885,3</t>
   </si>
   <si>
+    <t>индиго</t>
+  </si>
+  <si>
+    <t>кварц</t>
+  </si>
+  <si>
+    <t>кпб899-1</t>
+  </si>
+  <si>
+    <t>68,7</t>
+  </si>
+  <si>
+    <t>кпб947-1</t>
+  </si>
+  <si>
+    <t>кпб948-1</t>
+  </si>
+  <si>
+    <t>персик</t>
+  </si>
+  <si>
+    <t>902,2</t>
+  </si>
+  <si>
+    <t>пудра</t>
+  </si>
+  <si>
+    <t>455,3</t>
+  </si>
+  <si>
+    <t>сирень</t>
+  </si>
+  <si>
+    <t>853,4</t>
+  </si>
+  <si>
+    <t>Поплин</t>
+  </si>
+  <si>
+    <t>Маккиато</t>
+  </si>
+  <si>
+    <t>717-1</t>
+  </si>
+  <si>
+    <t>Маккиато (комп.)</t>
+  </si>
+  <si>
+    <t>718-1</t>
+  </si>
+  <si>
+    <t>Сияние (комп.)</t>
+  </si>
+  <si>
+    <t>743-1</t>
+  </si>
+  <si>
+    <t>451,1</t>
+  </si>
+  <si>
+    <t>743-2</t>
+  </si>
+  <si>
+    <t>1 031,5</t>
+  </si>
+  <si>
+    <t>Палермо</t>
+  </si>
+  <si>
+    <t>788-1</t>
+  </si>
+  <si>
+    <t>232,2</t>
+  </si>
+  <si>
+    <t>Дуновение (комп)</t>
+  </si>
+  <si>
+    <t>825-2</t>
+  </si>
+  <si>
+    <t>1 654,1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Пионы </t>
+  </si>
+  <si>
+    <t>876-1</t>
+  </si>
+  <si>
+    <t>1 914,2</t>
+  </si>
+  <si>
+    <t>Венди</t>
+  </si>
+  <si>
+    <t>959-1</t>
+  </si>
+  <si>
+    <t>151,4</t>
+  </si>
+  <si>
+    <t>Флирт</t>
+  </si>
+  <si>
+    <t>970-1</t>
+  </si>
+  <si>
+    <t>Букетики</t>
+  </si>
+  <si>
+    <t>973-1</t>
+  </si>
+  <si>
+    <t>787,6</t>
+  </si>
+  <si>
+    <t>Букетики (комп)</t>
+  </si>
+  <si>
+    <t>974-1</t>
+  </si>
+  <si>
+    <t>1 046,4</t>
+  </si>
+  <si>
+    <t>Малена</t>
+  </si>
+  <si>
+    <t>975-1</t>
+  </si>
+  <si>
+    <t>1 507,1</t>
+  </si>
+  <si>
+    <t>Малена (комп)</t>
+  </si>
+  <si>
+    <t>976-1</t>
+  </si>
+  <si>
+    <t>778,7</t>
+  </si>
+  <si>
+    <t>Вивальди</t>
+  </si>
+  <si>
+    <t>977-1</t>
+  </si>
+  <si>
+    <t>1 014,3</t>
+  </si>
+  <si>
+    <t>Вивальди (комп)</t>
+  </si>
+  <si>
+    <t>978-1</t>
+  </si>
+  <si>
+    <t>1 174</t>
+  </si>
+  <si>
+    <t>Лаванда</t>
+  </si>
+  <si>
+    <t>979-1</t>
+  </si>
+  <si>
+    <t>909,7</t>
+  </si>
+  <si>
+    <t>Колокольчики</t>
+  </si>
+  <si>
+    <t>981-1</t>
+  </si>
+  <si>
+    <t>1 247,5</t>
+  </si>
+  <si>
+    <t>Колокольчики (комп)</t>
+  </si>
+  <si>
+    <t>982-1</t>
+  </si>
+  <si>
+    <t>455,9</t>
+  </si>
+  <si>
+    <t>982-2</t>
+  </si>
+  <si>
+    <t>462,6</t>
+  </si>
+  <si>
+    <t>Арлекин</t>
+  </si>
+  <si>
+    <t>983-1</t>
+  </si>
+  <si>
+    <t>835,7</t>
+  </si>
+  <si>
+    <t>Конфитюр</t>
+  </si>
+  <si>
+    <t>988-1</t>
+  </si>
+  <si>
+    <t>894,6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Идиллия </t>
+  </si>
+  <si>
+    <t>989-1</t>
+  </si>
+  <si>
+    <t>Вишня</t>
+  </si>
+  <si>
+    <t>991-1</t>
+  </si>
+  <si>
+    <t>4 626,4</t>
+  </si>
+  <si>
+    <t>Сканди</t>
+  </si>
+  <si>
+    <t>992-1</t>
+  </si>
+  <si>
+    <t>521,3</t>
+  </si>
+  <si>
+    <t>Сканди (комп)</t>
+  </si>
+  <si>
+    <t>993-1</t>
+  </si>
+  <si>
+    <t>Денди</t>
+  </si>
+  <si>
+    <t>994-1</t>
+  </si>
+  <si>
+    <t>Денди (комп)</t>
+  </si>
+  <si>
+    <t>995-1</t>
+  </si>
+  <si>
+    <t>525,2</t>
+  </si>
+  <si>
+    <t>аквамарин</t>
+  </si>
+  <si>
+    <t>386,5</t>
+  </si>
+  <si>
+    <t>антрацит</t>
+  </si>
+  <si>
+    <t>атлантик</t>
+  </si>
+  <si>
+    <t>1 938</t>
+  </si>
+  <si>
+    <t>баклажан</t>
+  </si>
+  <si>
+    <t>2 012</t>
+  </si>
+  <si>
+    <t>бежевый</t>
+  </si>
+  <si>
+    <t>1 338,1</t>
+  </si>
+  <si>
     <t>брусника</t>
   </si>
   <si>
-    <t>1 482,5</t>
-  </si>
-  <si>
-    <t>кпб899-1</t>
-  </si>
-  <si>
-    <t>139,2</t>
-  </si>
-  <si>
-    <t>кпб948-1</t>
+    <t>890,3</t>
+  </si>
+  <si>
+    <t>голубой</t>
+  </si>
+  <si>
+    <t>горчица</t>
+  </si>
+  <si>
+    <t>1 501,9</t>
+  </si>
+  <si>
+    <t>графит</t>
+  </si>
+  <si>
+    <t>784,5</t>
+  </si>
+  <si>
+    <t>дельфин</t>
+  </si>
+  <si>
+    <t>изумруд</t>
+  </si>
+  <si>
+    <t>1 457,5</t>
+  </si>
+  <si>
+    <t>1 742,4</t>
+  </si>
+  <si>
+    <t>какао</t>
+  </si>
+  <si>
+    <t>1 137,3</t>
+  </si>
+  <si>
+    <t>1 228,7</t>
+  </si>
+  <si>
+    <t>кпб904-1</t>
+  </si>
+  <si>
+    <t>356,9</t>
+  </si>
+  <si>
+    <t>кпб906-1</t>
+  </si>
+  <si>
+    <t>кпб907-1</t>
+  </si>
+  <si>
+    <t>кпб908-1</t>
+  </si>
+  <si>
+    <t>269,4</t>
+  </si>
+  <si>
+    <t>кпб914-1</t>
+  </si>
+  <si>
+    <t>кпб914-5</t>
+  </si>
+  <si>
+    <t>2 473,2</t>
+  </si>
+  <si>
+    <t>кпб914-6</t>
+  </si>
+  <si>
+    <t>1 441</t>
+  </si>
+  <si>
+    <t>кпб924-1</t>
+  </si>
+  <si>
+    <t>красный 15-01</t>
+  </si>
+  <si>
+    <t>957,7</t>
+  </si>
+  <si>
+    <t>кремовый</t>
+  </si>
+  <si>
+    <t>122,5</t>
+  </si>
+  <si>
+    <t>лаванда</t>
+  </si>
+  <si>
+    <t>1 149</t>
+  </si>
+  <si>
+    <t>лазурный</t>
+  </si>
+  <si>
+    <t>1 558,7</t>
+  </si>
+  <si>
+    <t>лён</t>
+  </si>
+  <si>
+    <t>929,1</t>
+  </si>
+  <si>
+    <t>лимон</t>
+  </si>
+  <si>
+    <t>1 175,9</t>
+  </si>
+  <si>
+    <t>малина</t>
+  </si>
+  <si>
+    <t>ментол</t>
+  </si>
+  <si>
+    <t>834,4</t>
+  </si>
+  <si>
+    <t>мокко</t>
+  </si>
+  <si>
+    <t>1 686,5</t>
+  </si>
+  <si>
+    <t>мохито</t>
+  </si>
+  <si>
+    <t>689,5</t>
   </si>
   <si>
     <t>мята</t>
   </si>
   <si>
-    <t>1 494,4</t>
-  </si>
-  <si>
-    <t>персик</t>
-  </si>
-  <si>
-    <t>902,2</t>
-  </si>
-  <si>
-    <t>пудра</t>
-  </si>
-  <si>
-    <t>554,3</t>
-  </si>
-  <si>
-    <t>сирень</t>
-  </si>
-  <si>
-    <t>853,4</t>
-  </si>
-  <si>
-    <t>Поплин</t>
-  </si>
-  <si>
-    <t>Маккиато</t>
-  </si>
-  <si>
-    <t>717-1</t>
-  </si>
-  <si>
-    <t>624,2</t>
-  </si>
-  <si>
-    <t>Маккиато (комп.)</t>
-  </si>
-  <si>
-    <t>718-1</t>
-  </si>
-  <si>
-    <t>Сияние (комп.)</t>
-  </si>
-  <si>
-    <t>743-1</t>
-  </si>
-  <si>
-    <t>484,1</t>
-  </si>
-  <si>
-    <t>743-2</t>
-  </si>
-  <si>
-    <t>1 064,5</t>
-  </si>
-  <si>
-    <t>Палермо</t>
-  </si>
-  <si>
-    <t>788-1</t>
-  </si>
-  <si>
-    <t>524,1</t>
-  </si>
-  <si>
-    <t>Дуновение (комп)</t>
-  </si>
-  <si>
-    <t>825-2</t>
-  </si>
-  <si>
-    <t>1 852,1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Пионы </t>
-  </si>
-  <si>
-    <t>876-1</t>
-  </si>
-  <si>
-    <t>1 980,2</t>
-  </si>
-  <si>
-    <t>Венди</t>
-  </si>
-  <si>
-    <t>959-1</t>
-  </si>
-  <si>
-    <t>151,4</t>
-  </si>
-  <si>
-    <t>Флирт</t>
-  </si>
-  <si>
-    <t>970-1</t>
-  </si>
-  <si>
-    <t>Гармония</t>
-  </si>
-  <si>
-    <t>972-2</t>
-  </si>
-  <si>
-    <t>Букетики</t>
-  </si>
-  <si>
-    <t>973-1</t>
-  </si>
-  <si>
-    <t>1 225,6</t>
-  </si>
-  <si>
-    <t>Букетики (комп)</t>
-  </si>
-  <si>
-    <t>974-1</t>
-  </si>
-  <si>
-    <t>1 280,2</t>
-  </si>
-  <si>
-    <t>Малена</t>
-  </si>
-  <si>
-    <t>975-1</t>
-  </si>
-  <si>
-    <t>1 507,1</t>
-  </si>
-  <si>
-    <t>Малена (комп)</t>
-  </si>
-  <si>
-    <t>976-1</t>
-  </si>
-  <si>
-    <t>Вивальди</t>
-  </si>
-  <si>
-    <t>977-1</t>
-  </si>
-  <si>
-    <t>1 179,3</t>
-  </si>
-  <si>
-    <t>Вивальди (комп)</t>
-  </si>
-  <si>
-    <t>978-1</t>
-  </si>
-  <si>
-    <t>1 405</t>
-  </si>
-  <si>
-    <t>Лаванда</t>
-  </si>
-  <si>
-    <t>979-1</t>
-  </si>
-  <si>
-    <t>1 239,7</t>
-  </si>
-  <si>
-    <t>Колокольчики</t>
-  </si>
-  <si>
-    <t>981-1</t>
-  </si>
-  <si>
-    <t>1 280,5</t>
-  </si>
-  <si>
-    <t>Колокольчики (комп)</t>
-  </si>
-  <si>
-    <t>982-1</t>
-  </si>
-  <si>
-    <t>982-2</t>
-  </si>
-  <si>
-    <t>462,6</t>
-  </si>
-  <si>
-    <t>Арлекин</t>
-  </si>
-  <si>
-    <t>983-1</t>
-  </si>
-  <si>
-    <t>901,7</t>
-  </si>
-  <si>
-    <t>Конфитюр</t>
-  </si>
-  <si>
-    <t>988-1</t>
-  </si>
-  <si>
-    <t>1 154,8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Идиллия </t>
-  </si>
-  <si>
-    <t>989-1</t>
-  </si>
-  <si>
-    <t>Вишня</t>
-  </si>
-  <si>
-    <t>991-1</t>
-  </si>
-  <si>
-    <t>636,1</t>
-  </si>
-  <si>
-    <t>Сканди</t>
-  </si>
-  <si>
-    <t>992-1</t>
-  </si>
-  <si>
-    <t>521,3</t>
-  </si>
-  <si>
-    <t>Сканди (комп)</t>
-  </si>
-  <si>
-    <t>993-1</t>
-  </si>
-  <si>
-    <t>Денди</t>
-  </si>
-  <si>
-    <t>994-1</t>
-  </si>
-  <si>
-    <t>Денди (комп)</t>
-  </si>
-  <si>
-    <t>995-1</t>
-  </si>
-  <si>
-    <t>254,3</t>
-  </si>
-  <si>
-    <t>аквамарин</t>
-  </si>
-  <si>
-    <t>386,5</t>
-  </si>
-  <si>
-    <t>антрацит</t>
-  </si>
-  <si>
-    <t>1 670,5</t>
-  </si>
-  <si>
-    <t>баклажан</t>
-  </si>
-  <si>
-    <t>бежевый</t>
-  </si>
-  <si>
-    <t>776,6</t>
-  </si>
-  <si>
-    <t>1 557,3</t>
-  </si>
-  <si>
-    <t>винный</t>
-  </si>
-  <si>
-    <t>744,7</t>
-  </si>
-  <si>
-    <t>голубой</t>
-  </si>
-  <si>
-    <t>дельфин</t>
-  </si>
-  <si>
-    <t>изумруд</t>
-  </si>
-  <si>
-    <t>1 490,5</t>
-  </si>
-  <si>
-    <t>индиго</t>
-  </si>
-  <si>
-    <t>2 405,7</t>
-  </si>
-  <si>
-    <t>кпб904-1</t>
-  </si>
-  <si>
-    <t>585,5</t>
-  </si>
-  <si>
-    <t>кпб906-1</t>
-  </si>
-  <si>
-    <t>68,7</t>
-  </si>
-  <si>
-    <t>кпб907-1</t>
-  </si>
-  <si>
-    <t>кпб908-1</t>
-  </si>
-  <si>
-    <t>636,4</t>
-  </si>
-  <si>
-    <t>кпб914-1</t>
-  </si>
-  <si>
-    <t>кпб914-5</t>
-  </si>
-  <si>
-    <t>1 345,8</t>
-  </si>
-  <si>
-    <t>кпб914-6</t>
-  </si>
-  <si>
-    <t>7 340,6</t>
-  </si>
-  <si>
-    <t>кпб916-1</t>
-  </si>
-  <si>
-    <t>кпб924-1</t>
-  </si>
-  <si>
-    <t>кремовый</t>
-  </si>
-  <si>
-    <t>188,5</t>
-  </si>
-  <si>
-    <t>лаванда</t>
-  </si>
-  <si>
-    <t>1 479</t>
-  </si>
-  <si>
-    <t>лазурный</t>
-  </si>
-  <si>
-    <t>1 624,7</t>
-  </si>
-  <si>
-    <t>лимон</t>
-  </si>
-  <si>
-    <t>малина</t>
-  </si>
-  <si>
-    <t>ментол</t>
-  </si>
-  <si>
-    <t>834,4</t>
-  </si>
-  <si>
-    <t>мохито</t>
-  </si>
-  <si>
-    <t>689,5</t>
+    <t>1 995,7</t>
   </si>
   <si>
     <t>океан</t>
   </si>
   <si>
-    <t>682,6</t>
+    <t>352,6</t>
   </si>
   <si>
     <t>орех</t>
   </si>
   <si>
-    <t>984,2</t>
+    <t>357,2</t>
   </si>
   <si>
     <t>отбеленная</t>
   </si>
   <si>
-    <t>1 438,6</t>
+    <t>211,7</t>
   </si>
   <si>
     <t>пепельная роза</t>
   </si>
   <si>
+    <t>2 899</t>
+  </si>
+  <si>
     <t>розовый</t>
   </si>
   <si>
-    <t>409,6</t>
+    <t>244,6</t>
   </si>
   <si>
     <t>серый</t>
   </si>
   <si>
-    <t>844,6</t>
+    <t>547,6</t>
   </si>
   <si>
     <t>879,4</t>
@@ -622,31 +661,34 @@
     <t>солнечный</t>
   </si>
   <si>
-    <t>1 562</t>
+    <t>1 496</t>
   </si>
   <si>
     <t>тиффани</t>
   </si>
   <si>
-    <t>1 906,7</t>
+    <t>1 873,7</t>
   </si>
   <si>
     <t>фисташка</t>
   </si>
   <si>
-    <t>2 166,1</t>
+    <t>1 570,4</t>
+  </si>
+  <si>
+    <t>черника</t>
+  </si>
+  <si>
+    <t>1 982,5</t>
   </si>
   <si>
     <t>шампань</t>
   </si>
   <si>
-    <t>1 178,9</t>
-  </si>
-  <si>
-    <t>эвкалипт</t>
-  </si>
-  <si>
-    <t>447,5</t>
+    <t>эспрессо</t>
+  </si>
+  <si>
+    <t>1 446,8</t>
   </si>
 </sst>
 </file>
@@ -856,7 +898,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Рисунок 2" descr="546-1.jpg"/>
+        <xdr:cNvPr id="3" name="Рисунок 2" descr="532-1.jpg"/>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -894,7 +936,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Рисунок 3" descr="547-2.jpg"/>
+        <xdr:cNvPr id="4" name="Рисунок 3" descr="546-1.jpg"/>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -932,7 +974,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Рисунок 4" descr="554-1.jpg"/>
+        <xdr:cNvPr id="5" name="Рисунок 4" descr="547-2.jpg"/>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -970,7 +1012,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Рисунок 5" descr="624-1.jpg"/>
+        <xdr:cNvPr id="6" name="Рисунок 5" descr="554-1.jpg"/>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -1008,7 +1050,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="Рисунок 6" descr="625-1.jpg"/>
+        <xdr:cNvPr id="7" name="Рисунок 6" descr="624-1.jpg"/>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -1046,7 +1088,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="Рисунок 7" descr="761-1.jpg"/>
+        <xdr:cNvPr id="8" name="Рисунок 7" descr="625-1.jpg"/>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -1084,7 +1126,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="Рисунок 8" descr="761-2.jpg"/>
+        <xdr:cNvPr id="9" name="Рисунок 8" descr="761-1.jpg"/>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -1122,7 +1164,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="Рисунок 9" descr="812-1.jpg"/>
+        <xdr:cNvPr id="10" name="Рисунок 9" descr="761-2.jpg"/>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -1160,7 +1202,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="Рисунок 10" descr="813-1.jpg"/>
+        <xdr:cNvPr id="11" name="Рисунок 10" descr="812-1.jpg"/>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -1198,7 +1240,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="12" name="Рисунок 11" descr="821-2.jpg"/>
+        <xdr:cNvPr id="12" name="Рисунок 11" descr="813-1.jpg"/>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -1236,7 +1278,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="13" name="Рисунок 12" descr="870-2.jpg"/>
+        <xdr:cNvPr id="13" name="Рисунок 12" descr="821-2.jpg"/>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -1274,7 +1316,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="14" name="Рисунок 13" descr="871-2.jpg"/>
+        <xdr:cNvPr id="14" name="Рисунок 13" descr="870-2.jpg"/>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -1312,7 +1354,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="15" name="Рисунок 14" descr="884-1.jpg"/>
+        <xdr:cNvPr id="15" name="Рисунок 14" descr="871-2.jpg"/>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -1350,7 +1392,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="16" name="Рисунок 15" descr="984-1.jpg"/>
+        <xdr:cNvPr id="16" name="Рисунок 15" descr="884-1.jpg"/>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -1388,7 +1430,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="17" name="Рисунок 16" descr="985-1.jpg"/>
+        <xdr:cNvPr id="17" name="Рисунок 16" descr="885-1.jpg"/>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -1502,7 +1544,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="20" name="Рисунок 19" descr="брусника.jpg"/>
+        <xdr:cNvPr id="20" name="Рисунок 19" descr="индиго.jpg"/>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -1540,7 +1582,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="21" name="Рисунок 20" descr="кпб899-1.jpg"/>
+        <xdr:cNvPr id="21" name="Рисунок 20" descr="кварц.jpg"/>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -1578,7 +1620,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="22" name="Рисунок 21" descr="кпб948-1.jpg"/>
+        <xdr:cNvPr id="22" name="Рисунок 21" descr="кпб899-1.jpg"/>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -1616,7 +1658,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="23" name="Рисунок 22" descr="мята.jpg"/>
+        <xdr:cNvPr id="23" name="Рисунок 22" descr="кпб947-1.jpg"/>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -1654,7 +1696,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="24" name="Рисунок 23" descr="персик.jpg"/>
+        <xdr:cNvPr id="24" name="Рисунок 23" descr="кпб948-1.jpg"/>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -1692,7 +1734,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="25" name="Рисунок 24" descr="пудра.jpg"/>
+        <xdr:cNvPr id="25" name="Рисунок 24" descr="персик.jpg"/>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -1730,7 +1772,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="26" name="Рисунок 25" descr="сирень.jpg"/>
+        <xdr:cNvPr id="26" name="Рисунок 25" descr="пудра.jpg"/>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -1757,46 +1799,46 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>34</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="27" name="Рисунок 26" descr="сирень.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId26" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1847850" y="22555200"/>
+          <a:ext cx="1114425" cy="781050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>35</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="27" name="Рисунок 26" descr="717-1.jpg"/>
-        <xdr:cNvPicPr>
-          <a:picLocks/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId26" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1847850" y="22936200"/>
-          <a:ext cx="1114425" cy="781050"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
@@ -1806,7 +1848,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="28" name="Рисунок 27" descr="718-1.jpg"/>
+        <xdr:cNvPr id="28" name="Рисунок 27" descr="717-1.jpg"/>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -1844,7 +1886,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="29" name="Рисунок 28" descr="743-1.jpg"/>
+        <xdr:cNvPr id="29" name="Рисунок 28" descr="718-1.jpg"/>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -1882,7 +1924,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="30" name="Рисунок 29" descr="743-2.jpg"/>
+        <xdr:cNvPr id="30" name="Рисунок 29" descr="743-1.jpg"/>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -1920,7 +1962,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="31" name="Рисунок 30" descr="788-1.jpg"/>
+        <xdr:cNvPr id="31" name="Рисунок 30" descr="743-2.jpg"/>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -1958,7 +2000,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="32" name="Рисунок 31" descr="825-2.jpg"/>
+        <xdr:cNvPr id="32" name="Рисунок 31" descr="788-1.jpg"/>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -1996,7 +2038,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="33" name="Рисунок 32" descr="876-1.jpg"/>
+        <xdr:cNvPr id="33" name="Рисунок 32" descr="825-2.jpg"/>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -2034,7 +2076,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="34" name="Рисунок 33" descr="959-1.jpg"/>
+        <xdr:cNvPr id="34" name="Рисунок 33" descr="876-1.jpg"/>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -2072,7 +2114,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="35" name="Рисунок 34" descr="970-1.jpg"/>
+        <xdr:cNvPr id="35" name="Рисунок 34" descr="959-1.jpg"/>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -2110,7 +2152,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="36" name="Рисунок 35" descr="972-2.jpg"/>
+        <xdr:cNvPr id="36" name="Рисунок 35" descr="970-1.jpg"/>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -2908,7 +2950,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="57" name="Рисунок 56" descr="баклажан.jpg"/>
+        <xdr:cNvPr id="57" name="Рисунок 56" descr="атлантик.jpg"/>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -2946,7 +2988,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="58" name="Рисунок 57" descr="бежевый.jpg"/>
+        <xdr:cNvPr id="58" name="Рисунок 57" descr="баклажан.jpg"/>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -2984,7 +3026,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="59" name="Рисунок 58" descr="брусника.jpg"/>
+        <xdr:cNvPr id="59" name="Рисунок 58" descr="бежевый.jpg"/>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -3022,7 +3064,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="60" name="Рисунок 59" descr="винный.jpg"/>
+        <xdr:cNvPr id="60" name="Рисунок 59" descr="брусника.jpg"/>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -3098,7 +3140,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="62" name="Рисунок 61" descr="дельфин.jpg"/>
+        <xdr:cNvPr id="62" name="Рисунок 61" descr="горчица.jpg"/>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -3136,7 +3178,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="63" name="Рисунок 62" descr="изумруд.jpg"/>
+        <xdr:cNvPr id="63" name="Рисунок 62" descr="графит.jpg"/>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -3174,7 +3216,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="64" name="Рисунок 63" descr="индиго.jpg"/>
+        <xdr:cNvPr id="64" name="Рисунок 63" descr="дельфин.jpg"/>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -3212,7 +3254,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="65" name="Рисунок 64" descr="кпб904-1.jpg"/>
+        <xdr:cNvPr id="65" name="Рисунок 64" descr="изумруд.jpg"/>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -3250,7 +3292,45 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="66" name="Рисунок 65" descr="кпб906-1.jpg"/>
+        <xdr:cNvPr id="66" name="Рисунок 65" descr="индиго.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId19" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1847850" y="53397150"/>
+          <a:ext cx="1114425" cy="781050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="67" name="Рисунок 66" descr="какао.jpg"/>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -3263,32 +3343,32 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1847850" y="53397150"/>
-          <a:ext cx="1114425" cy="781050"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>74</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
+          <a:off x="1847850" y="54178200"/>
+          <a:ext cx="1114425" cy="781050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>75</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="67" name="Рисунок 66" descr="кпб907-1.jpg"/>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="68" name="Рисунок 67" descr="кварц.jpg"/>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -3301,32 +3381,32 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1847850" y="54178200"/>
-          <a:ext cx="1114425" cy="781050"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>75</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
+          <a:off x="1847850" y="54959250"/>
+          <a:ext cx="1114425" cy="781050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>76</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="68" name="Рисунок 67" descr="кпб908-1.jpg"/>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="69" name="Рисунок 68" descr="кпб904-1.jpg"/>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -3339,32 +3419,32 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1847850" y="54959250"/>
-          <a:ext cx="1114425" cy="781050"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>76</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
+          <a:off x="1847850" y="55740300"/>
+          <a:ext cx="1114425" cy="781050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>77</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="69" name="Рисунок 68" descr="кпб914-1.jpg"/>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="70" name="Рисунок 69" descr="кпб906-1.jpg"/>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -3377,32 +3457,32 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1847850" y="55740300"/>
-          <a:ext cx="1114425" cy="781050"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>77</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
+          <a:off x="1847850" y="56521350"/>
+          <a:ext cx="1114425" cy="781050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>78</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="70" name="Рисунок 69" descr="кпб914-5.jpg"/>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="71" name="Рисунок 70" descr="кпб907-1.jpg"/>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -3415,32 +3495,32 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1847850" y="56521350"/>
-          <a:ext cx="1114425" cy="781050"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>78</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
+          <a:off x="1847850" y="57302400"/>
+          <a:ext cx="1114425" cy="781050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>79</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="71" name="Рисунок 70" descr="кпб914-6.jpg"/>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>80</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="72" name="Рисунок 71" descr="кпб908-1.jpg"/>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -3453,32 +3533,32 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1847850" y="57302400"/>
-          <a:ext cx="1114425" cy="781050"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
+          <a:off x="1847850" y="58083450"/>
+          <a:ext cx="1114425" cy="781050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>80</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="72" name="Рисунок 71" descr="кпб916-1.jpg"/>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="73" name="Рисунок 72" descr="кпб914-1.jpg"/>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -3491,32 +3571,32 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1847850" y="58083450"/>
-          <a:ext cx="1114425" cy="781050"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>80</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
+          <a:off x="1847850" y="58864500"/>
+          <a:ext cx="1114425" cy="781050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>81</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="73" name="Рисунок 72" descr="кпб924-1.jpg"/>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="74" name="Рисунок 73" descr="кпб914-5.jpg"/>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -3529,32 +3609,32 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1847850" y="58864500"/>
-          <a:ext cx="1114425" cy="781050"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>81</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
+          <a:off x="1847850" y="59645550"/>
+          <a:ext cx="1114425" cy="781050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>82</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="74" name="Рисунок 73" descr="кремовый.jpg"/>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="75" name="Рисунок 74" descr="кпб914-6.jpg"/>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -3567,32 +3647,32 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1847850" y="59645550"/>
-          <a:ext cx="1114425" cy="781050"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>82</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
+          <a:off x="1847850" y="60426600"/>
+          <a:ext cx="1114425" cy="781050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>83</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="75" name="Рисунок 74" descr="лаванда.jpg"/>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="76" name="Рисунок 75" descr="кпб924-1.jpg"/>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -3605,32 +3685,32 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1847850" y="60426600"/>
-          <a:ext cx="1114425" cy="781050"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
+          <a:off x="1847850" y="61207650"/>
+          <a:ext cx="1114425" cy="781050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>84</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="76" name="Рисунок 75" descr="лазурный.jpg"/>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="77" name="Рисунок 76" descr="3046-1.jpg"/>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -3643,32 +3723,32 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1847850" y="61207650"/>
-          <a:ext cx="1114425" cy="781050"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>84</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
+          <a:off x="1847850" y="61988700"/>
+          <a:ext cx="1114425" cy="781050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>85</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="77" name="Рисунок 76" descr="лимон.jpg"/>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="78" name="Рисунок 77" descr="кремовый.jpg"/>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -3681,32 +3761,32 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1847850" y="61988700"/>
-          <a:ext cx="1114425" cy="781050"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>85</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
+          <a:off x="1847850" y="62769750"/>
+          <a:ext cx="1114425" cy="781050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>86</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="78" name="Рисунок 77" descr="малина.jpg"/>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="79" name="Рисунок 78" descr="лаванда.jpg"/>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -3719,32 +3799,32 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1847850" y="62769750"/>
-          <a:ext cx="1114425" cy="781050"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>86</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
+          <a:off x="1847850" y="63550800"/>
+          <a:ext cx="1114425" cy="781050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>87</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="79" name="Рисунок 78" descr="ментол.jpg"/>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>88</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="80" name="Рисунок 79" descr="лазурный.jpg"/>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -3757,32 +3837,32 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1847850" y="63550800"/>
-          <a:ext cx="1114425" cy="781050"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>87</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
+          <a:off x="1847850" y="64331850"/>
+          <a:ext cx="1114425" cy="781050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>88</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="80" name="Рисунок 79" descr="мохито.jpg"/>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>89</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="81" name="Рисунок 80" descr="лён.jpg"/>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -3795,32 +3875,32 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1847850" y="64331850"/>
-          <a:ext cx="1114425" cy="781050"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>88</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
+          <a:off x="1847850" y="65112900"/>
+          <a:ext cx="1114425" cy="781050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>89</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="81" name="Рисунок 80" descr="океан.jpg"/>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="82" name="Рисунок 81" descr="лимон.jpg"/>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -3833,32 +3913,32 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1847850" y="65112900"/>
-          <a:ext cx="1114425" cy="781050"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>89</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
+          <a:off x="1847850" y="65893950"/>
+          <a:ext cx="1114425" cy="781050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>90</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="82" name="Рисунок 81" descr="орех.jpg"/>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>91</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="83" name="Рисунок 82" descr="малина.jpg"/>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -3871,32 +3951,32 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1847850" y="65893950"/>
-          <a:ext cx="1114425" cy="781050"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>90</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
+          <a:off x="1847850" y="66675000"/>
+          <a:ext cx="1114425" cy="781050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>91</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="83" name="Рисунок 82" descr="отбеленная.jpg"/>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>92</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="84" name="Рисунок 83" descr="ментол.jpg"/>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -3909,32 +3989,32 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1847850" y="66675000"/>
-          <a:ext cx="1114425" cy="781050"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>91</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
+          <a:off x="1847850" y="67456050"/>
+          <a:ext cx="1114425" cy="781050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>92</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="84" name="Рисунок 83" descr="пепельная роза.jpg"/>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>93</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="85" name="Рисунок 84" descr="мокко.jpg"/>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -3947,32 +4027,32 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1847850" y="67456050"/>
-          <a:ext cx="1114425" cy="781050"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>92</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
+          <a:off x="1847850" y="68237100"/>
+          <a:ext cx="1114425" cy="781050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>93</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="85" name="Рисунок 84" descr="розовый.jpg"/>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>94</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="86" name="Рисунок 85" descr="мохито.jpg"/>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -3985,32 +4065,32 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1847850" y="68237100"/>
-          <a:ext cx="1114425" cy="781050"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>93</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
+          <a:off x="1847850" y="69018150"/>
+          <a:ext cx="1114425" cy="781050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>94</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="86" name="Рисунок 85" descr="серый.jpg"/>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>95</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="87" name="Рисунок 86" descr="мята.jpg"/>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -4023,32 +4103,32 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1847850" y="69018150"/>
-          <a:ext cx="1114425" cy="781050"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>94</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
+          <a:off x="1847850" y="69799200"/>
+          <a:ext cx="1114425" cy="781050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>95</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="87" name="Рисунок 86" descr="сирень.jpg"/>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>96</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="88" name="Рисунок 87" descr="океан.jpg"/>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -4061,32 +4141,32 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1847850" y="69799200"/>
-          <a:ext cx="1114425" cy="781050"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>95</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
+          <a:off x="1847850" y="70580250"/>
+          <a:ext cx="1114425" cy="781050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>96</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="88" name="Рисунок 87" descr="солнечный.jpg"/>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>97</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="89" name="Рисунок 88" descr="орех.jpg"/>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -4099,32 +4179,32 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1847850" y="70580250"/>
-          <a:ext cx="1114425" cy="781050"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>96</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
+          <a:off x="1847850" y="71361300"/>
+          <a:ext cx="1114425" cy="781050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>97</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="89" name="Рисунок 88" descr="тиффани.jpg"/>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>98</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="90" name="Рисунок 89" descr="отбеленная.jpg"/>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -4137,32 +4217,32 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1847850" y="71361300"/>
-          <a:ext cx="1114425" cy="781050"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>97</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
+          <a:off x="1847850" y="72142350"/>
+          <a:ext cx="1114425" cy="781050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>98</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="90" name="Рисунок 89" descr="фисташка.jpg"/>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>99</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="91" name="Рисунок 90" descr="пепельная роза.jpg"/>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -4175,32 +4255,32 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1847850" y="72142350"/>
-          <a:ext cx="1114425" cy="781050"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>98</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
+          <a:off x="1847850" y="72923400"/>
+          <a:ext cx="1114425" cy="781050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>99</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="91" name="Рисунок 90" descr="шампань.jpg"/>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>100</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="92" name="Рисунок 91" descr="пудра.jpg"/>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -4213,32 +4293,32 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1847850" y="72923400"/>
-          <a:ext cx="1114425" cy="781050"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>99</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
+          <a:off x="1847850" y="73704450"/>
+          <a:ext cx="1114425" cy="781050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>100</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="92" name="Рисунок 91" descr="эвкалипт.jpg"/>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>101</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="93" name="Рисунок 92" descr="розовый.jpg"/>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -4251,7 +4331,311 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1847850" y="73704450"/>
+          <a:off x="1847850" y="74485500"/>
+          <a:ext cx="1114425" cy="781050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>101</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>102</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="94" name="Рисунок 93" descr="серый.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId92" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1847850" y="75266550"/>
+          <a:ext cx="1114425" cy="781050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>102</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>103</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="95" name="Рисунок 94" descr="сирень.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId93" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1847850" y="76047600"/>
+          <a:ext cx="1114425" cy="781050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>103</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>104</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="96" name="Рисунок 95" descr="солнечный.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId94" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1847850" y="76828650"/>
+          <a:ext cx="1114425" cy="781050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>104</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>105</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="97" name="Рисунок 96" descr="тиффани.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId95" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1847850" y="77609700"/>
+          <a:ext cx="1114425" cy="781050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>105</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>106</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="98" name="Рисунок 97" descr="фисташка.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId96" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1847850" y="78390750"/>
+          <a:ext cx="1114425" cy="781050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>106</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>107</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="99" name="Рисунок 98" descr="черника.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId97" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1847850" y="79171800"/>
+          <a:ext cx="1114425" cy="781050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>107</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>108</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="100" name="Рисунок 99" descr="шампань.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId98" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1847850" y="79952850"/>
+          <a:ext cx="1114425" cy="781050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>108</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>109</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="101" name="Рисунок 100" descr="эспрессо.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId99" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1847850" y="80733900"/>
           <a:ext cx="1114425" cy="781050"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4276,13 +4660,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="93" name="Рисунок 92" descr="ЛоготипТрадицииТекстиля2.jpg"/>
-        <xdr:cNvPicPr>
-          <a:picLocks/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId92" cstate="print"/>
+        <xdr:cNvPr id="102" name="Рисунок 101" descr="ЛоготипТрадицииТекстиля2.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId100" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4587,7 +4971,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D100"/>
+  <dimension ref="A1:D109"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="27.7109375" customWidth="1"/>
@@ -4734,116 +5118,116 @@
       <c r="C15" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="D15" s="10">
-        <v>84</v>
+      <c r="D15" s="10" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="61.5" customHeight="1">
       <c r="A16" s="10" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B16" s="9"/>
       <c r="C16" s="11" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="61.5" customHeight="1">
       <c r="A17" s="10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B17" s="9"/>
       <c r="C17" s="11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="61.5" customHeight="1">
       <c r="A18" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B18" s="9"/>
       <c r="C18" s="11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="61.5" customHeight="1">
       <c r="A19" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B19" s="9"/>
       <c r="C19" s="11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="61.5" customHeight="1">
       <c r="A20" s="10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B20" s="9"/>
       <c r="C20" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="D20" s="10">
-        <v>429</v>
+        <v>42</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="61.5" customHeight="1">
       <c r="A21" s="10" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B21" s="9"/>
       <c r="C21" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="D21" s="10" t="s">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="D21" s="10">
+        <v>429</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="61.5" customHeight="1">
       <c r="A22" s="10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B22" s="9"/>
       <c r="C22" s="11" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="61.5" customHeight="1">
       <c r="A23" s="10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B23" s="9"/>
       <c r="C23" s="11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="61.5" customHeight="1">
       <c r="A24" s="10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B24" s="9"/>
       <c r="C24" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="D24" s="10" t="s">
         <v>53</v>
+      </c>
+      <c r="D24" s="10">
+        <v>198</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="61.5" customHeight="1">
@@ -4874,349 +5258,347 @@
       <c r="C27" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="D27" s="10" t="s">
-        <v>60</v>
+      <c r="D27" s="10">
+        <v>429</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="61.5" customHeight="1">
       <c r="A28" s="10"/>
       <c r="B28" s="9"/>
       <c r="C28" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="D28" s="10" t="s">
-        <v>62</v>
+        <v>60</v>
+      </c>
+      <c r="D28" s="10">
+        <v>264</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="61.5" customHeight="1">
       <c r="A29" s="10"/>
       <c r="B29" s="9"/>
       <c r="C29" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="D29" s="10">
-        <v>392</v>
+        <v>61</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="61.5" customHeight="1">
       <c r="A30" s="10"/>
       <c r="B30" s="9"/>
       <c r="C30" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="D30" s="10" t="s">
-        <v>65</v>
+        <v>63</v>
+      </c>
+      <c r="D30" s="10">
+        <v>297</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="61.5" customHeight="1">
       <c r="A31" s="10"/>
       <c r="B31" s="9"/>
       <c r="C31" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="D31" s="10" t="s">
-        <v>67</v>
+        <v>64</v>
+      </c>
+      <c r="D31" s="10">
+        <v>392</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="61.5" customHeight="1">
       <c r="A32" s="10"/>
       <c r="B32" s="9"/>
       <c r="C32" s="11" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="61.5" customHeight="1">
       <c r="A33" s="10"/>
       <c r="B33" s="9"/>
       <c r="C33" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="D33" s="10" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="61.5" customHeight="1">
+      <c r="A34" s="10"/>
+      <c r="B34" s="9"/>
+      <c r="C34" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="D34" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="D33" s="10" t="s">
+    </row>
+    <row r="35" spans="1:4" ht="30" customHeight="1">
+      <c r="A35" s="8" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" ht="30" customHeight="1">
-      <c r="A34" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="B34" s="7"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="7"/>
-    </row>
-    <row r="35" spans="1:4" ht="61.5" customHeight="1">
-      <c r="A35" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="B35" s="9"/>
-      <c r="C35" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="D35" s="10" t="s">
-        <v>75</v>
-      </c>
+      <c r="B35" s="7"/>
+      <c r="C35" s="7"/>
+      <c r="D35" s="7"/>
     </row>
     <row r="36" spans="1:4" ht="61.5" customHeight="1">
       <c r="A36" s="10" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B36" s="9"/>
       <c r="C36" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D36" s="10">
-        <v>542</v>
+        <v>561</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="61.5" customHeight="1">
       <c r="A37" s="10" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B37" s="9"/>
       <c r="C37" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="D37" s="10" t="s">
-        <v>80</v>
+        <v>75</v>
+      </c>
+      <c r="D37" s="10">
+        <v>146</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="61.5" customHeight="1">
       <c r="A38" s="10" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B38" s="9"/>
       <c r="C38" s="11" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D38" s="10" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="61.5" customHeight="1">
       <c r="A39" s="10" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="B39" s="9"/>
       <c r="C39" s="11" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="D39" s="10" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="61.5" customHeight="1">
       <c r="A40" s="10" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="B40" s="9"/>
       <c r="C40" s="11" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="D40" s="10" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="61.5" customHeight="1">
       <c r="A41" s="10" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="B41" s="9"/>
       <c r="C41" s="11" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D41" s="10" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="61.5" customHeight="1">
       <c r="A42" s="10" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="B42" s="9"/>
       <c r="C42" s="11" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="D42" s="10" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="61.5" customHeight="1">
       <c r="A43" s="10" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B43" s="9"/>
       <c r="C43" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="D43" s="10">
-        <v>740</v>
+        <v>91</v>
+      </c>
+      <c r="D43" s="10" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="61.5" customHeight="1">
       <c r="A44" s="10" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B44" s="9"/>
       <c r="C44" s="11" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D44" s="10">
-        <v>265</v>
+        <v>674</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="61.5" customHeight="1">
       <c r="A45" s="10" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B45" s="9"/>
       <c r="C45" s="11" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D45" s="10" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="61.5" customHeight="1">
       <c r="A46" s="10" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B46" s="9"/>
       <c r="C46" s="11" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D46" s="10" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="61.5" customHeight="1">
       <c r="A47" s="10" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B47" s="9"/>
       <c r="C47" s="11" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D47" s="10" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="61.5" customHeight="1">
       <c r="A48" s="10" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B48" s="9"/>
       <c r="C48" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="D48" s="10">
-        <v>979</v>
+        <v>105</v>
+      </c>
+      <c r="D48" s="10" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="61.5" customHeight="1">
       <c r="A49" s="10" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B49" s="9"/>
       <c r="C49" s="11" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D49" s="10" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="61.5" customHeight="1">
       <c r="A50" s="10" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B50" s="9"/>
       <c r="C50" s="11" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D50" s="10" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="61.5" customHeight="1">
       <c r="A51" s="10" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B51" s="9"/>
       <c r="C51" s="11" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D51" s="10" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="61.5" customHeight="1">
       <c r="A52" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B52" s="9"/>
       <c r="C52" s="11" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D52" s="10" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="61.5" customHeight="1">
       <c r="A53" s="10" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B53" s="9"/>
       <c r="C53" s="11" t="s">
-        <v>123</v>
-      </c>
-      <c r="D53" s="10">
-        <v>658</v>
+        <v>120</v>
+      </c>
+      <c r="D53" s="10" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="61.5" customHeight="1">
       <c r="A54" s="10" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B54" s="9"/>
       <c r="C54" s="11" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D54" s="10" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="61.5" customHeight="1">
       <c r="A55" s="10" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B55" s="9"/>
       <c r="C55" s="11" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D55" s="10" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="61.5" customHeight="1">
       <c r="A56" s="10" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B56" s="9"/>
       <c r="C56" s="11" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D56" s="10" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="61.5" customHeight="1">
       <c r="A57" s="10" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B57" s="9"/>
       <c r="C57" s="11" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D57" s="10">
         <v>462</v>
@@ -5224,35 +5606,35 @@
     </row>
     <row r="58" spans="1:4" ht="61.5" customHeight="1">
       <c r="A58" s="10" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B58" s="9"/>
       <c r="C58" s="11" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D58" s="10" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="61.5" customHeight="1">
       <c r="A59" s="10" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B59" s="9"/>
       <c r="C59" s="11" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D59" s="10" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="60" spans="1:4" ht="61.5" customHeight="1">
       <c r="A60" s="10" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B60" s="9"/>
       <c r="C60" s="11" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D60" s="10">
         <v>528</v>
@@ -5260,106 +5642,106 @@
     </row>
     <row r="61" spans="1:4" ht="61.5" customHeight="1">
       <c r="A61" s="10" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B61" s="9"/>
       <c r="C61" s="11" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D61" s="10">
-        <v>680</v>
+        <v>679</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="61.5" customHeight="1">
       <c r="A62" s="10" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B62" s="9"/>
       <c r="C62" s="11" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D62" s="10" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="63" spans="1:4" ht="61.5" customHeight="1">
       <c r="A63" s="10"/>
       <c r="B63" s="9"/>
       <c r="C63" s="11" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D63" s="10" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="64" spans="1:4" ht="61.5" customHeight="1">
       <c r="A64" s="10"/>
       <c r="B64" s="9"/>
       <c r="C64" s="11" t="s">
-        <v>149</v>
-      </c>
-      <c r="D64" s="10" t="s">
-        <v>150</v>
+        <v>147</v>
+      </c>
+      <c r="D64" s="10">
+        <v>874</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="61.5" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="9"/>
       <c r="C65" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="D65" s="10">
-        <v>99</v>
+        <v>148</v>
+      </c>
+      <c r="D65" s="10" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="61.5" customHeight="1">
       <c r="A66" s="10"/>
       <c r="B66" s="9"/>
       <c r="C66" s="11" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D66" s="10" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="61.5" customHeight="1">
       <c r="A67" s="10"/>
       <c r="B67" s="9"/>
       <c r="C67" s="11" t="s">
-        <v>59</v>
+        <v>152</v>
       </c>
       <c r="D67" s="10" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="68" spans="1:4" ht="61.5" customHeight="1">
       <c r="A68" s="10"/>
       <c r="B68" s="9"/>
       <c r="C68" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="D68" s="10" t="s">
         <v>155</v>
-      </c>
-      <c r="D68" s="10" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="61.5" customHeight="1">
       <c r="A69" s="10"/>
       <c r="B69" s="9"/>
       <c r="C69" s="11" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D69" s="10">
-        <v>600</v>
+        <v>331</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="61.5" customHeight="1">
       <c r="A70" s="10"/>
       <c r="B70" s="9"/>
       <c r="C70" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="D70" s="10" t="s">
         <v>158</v>
-      </c>
-      <c r="D70" s="10">
-        <v>233</v>
       </c>
     </row>
     <row r="71" spans="1:4" ht="61.5" customHeight="1">
@@ -5378,235 +5760,235 @@
       <c r="C72" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="D72" s="10" t="s">
-        <v>162</v>
+      <c r="D72" s="10">
+        <v>134</v>
       </c>
     </row>
     <row r="73" spans="1:4" ht="61.5" customHeight="1">
       <c r="A73" s="10"/>
       <c r="B73" s="9"/>
       <c r="C73" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="D73" s="10" t="s">
         <v>163</v>
-      </c>
-      <c r="D73" s="10" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="74" spans="1:4" ht="61.5" customHeight="1">
       <c r="A74" s="10"/>
       <c r="B74" s="9"/>
       <c r="C74" s="11" t="s">
-        <v>165</v>
+        <v>59</v>
       </c>
       <c r="D74" s="10" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="75" spans="1:4" ht="61.5" customHeight="1">
       <c r="A75" s="10"/>
       <c r="B75" s="9"/>
       <c r="C75" s="11" t="s">
-        <v>167</v>
-      </c>
-      <c r="D75" s="10">
-        <v>686</v>
+        <v>165</v>
+      </c>
+      <c r="D75" s="10" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="76" spans="1:4" ht="61.5" customHeight="1">
       <c r="A76" s="10"/>
       <c r="B76" s="9"/>
       <c r="C76" s="11" t="s">
-        <v>168</v>
+        <v>60</v>
       </c>
       <c r="D76" s="10" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="77" spans="1:4" ht="61.5" customHeight="1">
       <c r="A77" s="10"/>
       <c r="B77" s="9"/>
       <c r="C77" s="11" t="s">
-        <v>170</v>
-      </c>
-      <c r="D77" s="10">
-        <v>767</v>
+        <v>168</v>
+      </c>
+      <c r="D77" s="10" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="78" spans="1:4" ht="61.5" customHeight="1">
       <c r="A78" s="10"/>
       <c r="B78" s="9"/>
       <c r="C78" s="11" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D78" s="10" t="s">
-        <v>172</v>
+        <v>62</v>
       </c>
     </row>
     <row r="79" spans="1:4" ht="61.5" customHeight="1">
       <c r="A79" s="10"/>
       <c r="B79" s="9"/>
       <c r="C79" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="D79" s="10" t="s">
-        <v>174</v>
+        <v>171</v>
+      </c>
+      <c r="D79" s="10">
+        <v>653</v>
       </c>
     </row>
     <row r="80" spans="1:4" ht="61.5" customHeight="1">
       <c r="A80" s="10"/>
       <c r="B80" s="9"/>
       <c r="C80" s="11" t="s">
-        <v>175</v>
-      </c>
-      <c r="D80" s="10">
-        <v>432</v>
+        <v>172</v>
+      </c>
+      <c r="D80" s="10" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="81" spans="1:4" ht="61.5" customHeight="1">
       <c r="A81" s="10"/>
       <c r="B81" s="9"/>
       <c r="C81" s="11" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D81" s="10">
-        <v>400</v>
+        <v>470</v>
       </c>
     </row>
     <row r="82" spans="1:4" ht="61.5" customHeight="1">
       <c r="A82" s="10"/>
       <c r="B82" s="9"/>
       <c r="C82" s="11" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D82" s="10" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="83" spans="1:4" ht="61.5" customHeight="1">
       <c r="A83" s="10"/>
       <c r="B83" s="9"/>
       <c r="C83" s="11" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D83" s="10" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="84" spans="1:4" ht="61.5" customHeight="1">
       <c r="A84" s="10"/>
       <c r="B84" s="9"/>
       <c r="C84" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="D84" s="10" t="s">
-        <v>182</v>
+        <v>179</v>
+      </c>
+      <c r="D84" s="10">
+        <v>350</v>
       </c>
     </row>
     <row r="85" spans="1:4" ht="61.5" customHeight="1">
       <c r="A85" s="10"/>
       <c r="B85" s="9"/>
       <c r="C85" s="11" t="s">
-        <v>183</v>
-      </c>
-      <c r="D85" s="10">
-        <v>460</v>
+        <v>180</v>
+      </c>
+      <c r="D85" s="10" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="86" spans="1:4" ht="61.5" customHeight="1">
       <c r="A86" s="10"/>
       <c r="B86" s="9"/>
       <c r="C86" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="D86" s="10">
-        <v>132</v>
+        <v>182</v>
+      </c>
+      <c r="D86" s="10" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="87" spans="1:4" ht="61.5" customHeight="1">
       <c r="A87" s="10"/>
       <c r="B87" s="9"/>
       <c r="C87" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="D87" s="10" t="s">
         <v>185</v>
-      </c>
-      <c r="D87" s="10" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="88" spans="1:4" ht="61.5" customHeight="1">
       <c r="A88" s="10"/>
       <c r="B88" s="9"/>
       <c r="C88" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D88" s="10" t="s">
         <v>187</v>
-      </c>
-      <c r="D88" s="10" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="89" spans="1:4" ht="61.5" customHeight="1">
       <c r="A89" s="10"/>
       <c r="B89" s="9"/>
       <c r="C89" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="D89" s="10" t="s">
         <v>189</v>
-      </c>
-      <c r="D89" s="10" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="90" spans="1:4" ht="61.5" customHeight="1">
       <c r="A90" s="10"/>
       <c r="B90" s="9"/>
       <c r="C90" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="D90" s="10" t="s">
         <v>191</v>
-      </c>
-      <c r="D90" s="10" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="91" spans="1:4" ht="61.5" customHeight="1">
       <c r="A91" s="10"/>
       <c r="B91" s="9"/>
       <c r="C91" s="11" t="s">
-        <v>193</v>
-      </c>
-      <c r="D91" s="10" t="s">
-        <v>194</v>
+        <v>192</v>
+      </c>
+      <c r="D91" s="10">
+        <v>132</v>
       </c>
     </row>
     <row r="92" spans="1:4" ht="61.5" customHeight="1">
       <c r="A92" s="10"/>
       <c r="B92" s="9"/>
       <c r="C92" s="11" t="s">
-        <v>195</v>
-      </c>
-      <c r="D92" s="10">
-        <v>401</v>
+        <v>193</v>
+      </c>
+      <c r="D92" s="10" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="93" spans="1:4" ht="61.5" customHeight="1">
       <c r="A93" s="10"/>
       <c r="B93" s="9"/>
       <c r="C93" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="D93" s="10" t="s">
         <v>196</v>
-      </c>
-      <c r="D93" s="10" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="94" spans="1:4" ht="61.5" customHeight="1">
       <c r="A94" s="10"/>
       <c r="B94" s="9"/>
       <c r="C94" s="11" t="s">
+        <v>197</v>
+      </c>
+      <c r="D94" s="10" t="s">
         <v>198</v>
-      </c>
-      <c r="D94" s="10" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="95" spans="1:4" ht="61.5" customHeight="1">
       <c r="A95" s="10"/>
       <c r="B95" s="9"/>
       <c r="C95" s="11" t="s">
-        <v>70</v>
+        <v>199</v>
       </c>
       <c r="D95" s="10" t="s">
         <v>200</v>
@@ -5648,18 +6030,108 @@
       <c r="C99" s="11" t="s">
         <v>207</v>
       </c>
-      <c r="D99" s="10" t="s">
-        <v>208</v>
+      <c r="D99" s="10">
+        <v>401</v>
       </c>
     </row>
     <row r="100" spans="1:4" ht="61.5" customHeight="1">
       <c r="A100" s="10"/>
       <c r="B100" s="9"/>
       <c r="C100" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="D100" s="10" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" ht="61.5" customHeight="1">
+      <c r="A101" s="10"/>
+      <c r="B101" s="9"/>
+      <c r="C101" s="11" t="s">
         <v>209</v>
       </c>
-      <c r="D100" s="10" t="s">
+      <c r="D101" s="10" t="s">
         <v>210</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" ht="61.5" customHeight="1">
+      <c r="A102" s="10"/>
+      <c r="B102" s="9"/>
+      <c r="C102" s="11" t="s">
+        <v>211</v>
+      </c>
+      <c r="D102" s="10" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" ht="61.5" customHeight="1">
+      <c r="A103" s="10"/>
+      <c r="B103" s="9"/>
+      <c r="C103" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="D103" s="10" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" ht="61.5" customHeight="1">
+      <c r="A104" s="10"/>
+      <c r="B104" s="9"/>
+      <c r="C104" s="11" t="s">
+        <v>214</v>
+      </c>
+      <c r="D104" s="10" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" ht="61.5" customHeight="1">
+      <c r="A105" s="10"/>
+      <c r="B105" s="9"/>
+      <c r="C105" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="D105" s="10" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" ht="61.5" customHeight="1">
+      <c r="A106" s="10"/>
+      <c r="B106" s="9"/>
+      <c r="C106" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="D106" s="10" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" ht="61.5" customHeight="1">
+      <c r="A107" s="10"/>
+      <c r="B107" s="9"/>
+      <c r="C107" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="D107" s="10" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" ht="61.5" customHeight="1">
+      <c r="A108" s="10"/>
+      <c r="B108" s="9"/>
+      <c r="C108" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="D108" s="10">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" ht="61.5" customHeight="1">
+      <c r="A109" s="10"/>
+      <c r="B109" s="9"/>
+      <c r="C109" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="D109" s="10" t="s">
+        <v>224</v>
       </c>
     </row>
   </sheetData>
